--- a/output_plant/stomata_Intermediate_liang_2022a.xlsx
+++ b/output_plant/stomata_Intermediate_liang_2022a.xlsx
@@ -609,7 +609,7 @@
     <t xml:space="preserve">10.1016/j.gloplacha.2022.103737</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/stomata-franks_liang_2022a.xlsx</t>
+    <t xml:space="preserve">stomata-franks_liang_2022a_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -678,7 +678,7 @@
     <t xml:space="preserve">BU19030917-1</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/stomata-sd_liang_2022a.xlsx</t>
+    <t xml:space="preserve">stomata-sd_liang_2022a_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">SD error (+/- 1 s.e.m.); 4 leaves</t>

--- a/output_plant/stomata_Intermediate_liang_2022a.xlsx
+++ b/output_plant/stomata_Intermediate_liang_2022a.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
   <si>
     <t>eDab</t>
   </si>
@@ -643,6 +643,9 @@
   </si>
   <si>
     <t xml:space="preserve">value from Franks et al. (2014; their Table S1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source used fixed photosynthesis (fixed_A=yes); A0 is the reported net photosynthetic rate.</t>
   </si>
   <si>
     <t xml:space="preserve">BU19073045</t>
@@ -2167,11 +2170,13 @@
       <c r="BJ5" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="BK5" s="1"/>
+      <c r="BK5" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>197</v>
@@ -2352,11 +2357,13 @@
       <c r="BJ6" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="BK6" s="1"/>
+      <c r="BK6" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>197</v>
@@ -2537,11 +2544,13 @@
       <c r="BJ7" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="BK7" s="1"/>
+      <c r="BK7" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>197</v>
@@ -2722,11 +2731,13 @@
       <c r="BJ8" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="BK8" s="1"/>
+      <c r="BK8" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>197</v>
@@ -2907,11 +2918,13 @@
       <c r="BJ9" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="BK9" s="1"/>
+      <c r="BK9" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>197</v>
@@ -3092,11 +3105,13 @@
       <c r="BJ10" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="BK10" s="1"/>
+      <c r="BK10" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>197</v>
@@ -3130,13 +3145,13 @@
         <v>201</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>203</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P11" s="26" t="n">
         <v>47505591.04</v>
@@ -3277,11 +3292,13 @@
       <c r="BJ11" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="BK11" s="1"/>
+      <c r="BK11" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>197</v>
@@ -3315,13 +3332,13 @@
         <v>201</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>203</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P12" s="26" t="n">
         <v>58970000</v>
@@ -3462,11 +3479,13 @@
       <c r="BJ12" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="BK12" s="1"/>
+      <c r="BK12" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>197</v>
@@ -3500,13 +3519,13 @@
         <v>201</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>203</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P13" s="26" t="n">
         <v>45230000</v>
@@ -3647,11 +3666,13 @@
       <c r="BJ13" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="BK13" s="1"/>
+      <c r="BK13" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>197</v>
@@ -3685,13 +3706,13 @@
         <v>201</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>203</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P14" s="26" t="n">
         <v>63426375.74</v>
@@ -3832,7 +3853,9 @@
       <c r="BJ14" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="BK14" s="1"/>
+      <c r="BK14" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15"/>
@@ -3840,7 +3863,7 @@
         <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D15" t="s">
         <v>199</v>
@@ -3868,13 +3891,13 @@
         <v>201</v>
       </c>
       <c r="M15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N15" t="s">
         <v>203</v>
       </c>
       <c r="O15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P15" t="n">
         <v>150100000</v>
@@ -3883,7 +3906,7 @@
         <v>57200000</v>
       </c>
       <c r="R15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="S15"/>
       <c r="T15"/>
@@ -3930,7 +3953,7 @@
       <c r="BI15"/>
       <c r="BJ15"/>
       <c r="BK15" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16">
